--- a/artfynd/A 22778-2026 artfynd.xlsx
+++ b/artfynd/A 22778-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -923,6 +923,658 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>133737117</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58444</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Mickelsjö, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>501330</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6796379</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>133737115</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58641</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Mickelsjö, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>501330</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6796379</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>133737114</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58134</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>102623</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Trädlärka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lullula arborea</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Mickelsjö, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>501330</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6796379</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>133737118</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Mickelsjö, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>501131</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6796399</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>133737119</v>
+      </c>
+      <c r="B8" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Mickelsjö, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>501129</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6796400</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>133737121</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Mickelsjö, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>501026</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6796396</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22778-2026 artfynd.xlsx
+++ b/artfynd/A 22778-2026 artfynd.xlsx
@@ -925,32 +925,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133737117</v>
+        <v>133737115</v>
       </c>
       <c r="B4" t="n">
-        <v>58444</v>
+        <v>58641</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103018</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -995,7 +995,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,27 +1032,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133737115</v>
+        <v>133737118</v>
       </c>
       <c r="B5" t="n">
-        <v>58641</v>
+        <v>57955</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103044</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1067,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>501330</v>
+        <v>501131</v>
       </c>
       <c r="R5" t="n">
-        <v>6796379</v>
+        <v>6796399</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,7 +1112,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,32 +1144,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133737114</v>
+        <v>133737112</v>
       </c>
       <c r="B6" t="n">
-        <v>58134</v>
+        <v>58444</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102623</v>
+        <v>103018</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1209,7 +1214,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1219,7 +1224,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1246,32 +1251,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133737118</v>
+        <v>133738645</v>
       </c>
       <c r="B7" t="n">
-        <v>57955</v>
+        <v>8455</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1281,10 +1286,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>501131</v>
+        <v>501129</v>
       </c>
       <c r="R7" t="n">
-        <v>6796399</v>
+        <v>6796400</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1329,11 +1334,6 @@
           <t>11:42</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1351,17 +1351,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133737119</v>
+        <v>133738639</v>
       </c>
       <c r="B8" t="n">
-        <v>8455</v>
+        <v>58134</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,21 +1369,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>102623</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1393,10 +1393,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>501129</v>
+        <v>501330</v>
       </c>
       <c r="R8" t="n">
-        <v>6796400</v>
+        <v>6796379</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1458,14 +1458,14 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133737121</v>
+        <v>133738647</v>
       </c>
       <c r="B9" t="n">
         <v>57955</v>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 22778-2026 artfynd.xlsx
+++ b/artfynd/A 22778-2026 artfynd.xlsx
@@ -928,7 +928,7 @@
         <v>133737115</v>
       </c>
       <c r="B4" t="n">
-        <v>58641</v>
+        <v>58648</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>133737118</v>
       </c>
       <c r="B5" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>133737112</v>
       </c>
       <c r="B6" t="n">
-        <v>58444</v>
+        <v>58451</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>133738645</v>
       </c>
       <c r="B7" t="n">
-        <v>8455</v>
+        <v>8460</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>133738639</v>
       </c>
       <c r="B8" t="n">
-        <v>58134</v>
+        <v>58141</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>133738647</v>
       </c>
       <c r="B9" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22778-2026 artfynd.xlsx
+++ b/artfynd/A 22778-2026 artfynd.xlsx
@@ -928,7 +928,7 @@
         <v>133737115</v>
       </c>
       <c r="B4" t="n">
-        <v>58648</v>
+        <v>58658</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>133737118</v>
       </c>
       <c r="B5" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>133737112</v>
       </c>
       <c r="B6" t="n">
-        <v>58451</v>
+        <v>58461</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>133738639</v>
       </c>
       <c r="B8" t="n">
-        <v>58141</v>
+        <v>58151</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>133738647</v>
       </c>
       <c r="B9" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22778-2026 artfynd.xlsx
+++ b/artfynd/A 22778-2026 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>95887562</v>
       </c>
       <c r="B2" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -726,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>501083.5955609002</v>
+        <v>501083</v>
       </c>
       <c r="R2" t="n">
-        <v>6796383.639567066</v>
+        <v>6796383</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,19 +754,9 @@
           <t>2021-09-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-09-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -807,12 +792,7 @@
         <v>98959535</v>
       </c>
       <c r="B3" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -853,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>501083.5949657349</v>
+        <v>501083</v>
       </c>
       <c r="R3" t="n">
-        <v>6796385.561570202</v>
+        <v>6796386</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,19 +866,9 @@
           <t>2021-09-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-09-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133737115</v>
+        <v>133737118</v>
       </c>
       <c r="B4" t="n">
-        <v>58658</v>
+        <v>57972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -936,16 +906,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -960,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>501330</v>
+        <v>501131</v>
       </c>
       <c r="R4" t="n">
-        <v>6796379</v>
+        <v>6796399</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -995,7 +965,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1005,7 +975,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,14 +1007,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133737118</v>
+        <v>133738647</v>
       </c>
       <c r="B5" t="n">
         <v>57972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1067,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>501131</v>
+        <v>501026</v>
       </c>
       <c r="R5" t="n">
-        <v>6796399</v>
+        <v>6796396</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1102,7 +1077,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,7 +1087,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1137,39 +1112,39 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133737112</v>
+        <v>133738639</v>
       </c>
       <c r="B6" t="n">
-        <v>58461</v>
+        <v>58151</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103018</v>
+        <v>102623</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1214,7 +1189,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1224,7 +1199,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,17 +1219,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133738645</v>
+        <v>133737112</v>
       </c>
       <c r="B7" t="n">
-        <v>8460</v>
+        <v>58461</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,21 +1237,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>103018</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1286,10 +1261,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>501129</v>
+        <v>501330</v>
       </c>
       <c r="R7" t="n">
-        <v>6796400</v>
+        <v>6796379</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1321,7 +1296,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1331,7 +1306,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,17 +1326,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133738639</v>
+        <v>133737115</v>
       </c>
       <c r="B8" t="n">
-        <v>58151</v>
+        <v>58658</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,16 +1344,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102623</v>
+        <v>103044</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1458,39 +1433,39 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133738647</v>
+        <v>133738645</v>
       </c>
       <c r="B9" t="n">
-        <v>57972</v>
+        <v>8460</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1500,10 +1475,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>501026</v>
+        <v>501129</v>
       </c>
       <c r="R9" t="n">
-        <v>6796396</v>
+        <v>6796400</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1535,7 +1510,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1545,12 +1520,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:57</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 22778-2026 artfynd.xlsx
+++ b/artfynd/A 22778-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95887562</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98959535</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1004,6 +1019,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133737118</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133738647</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1223,6 +1248,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133738639</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1330,6 +1360,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133737112</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1437,6 +1472,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133737115</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1544,8 +1584,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133738645</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>